--- a/rirekisyo.xlsx
+++ b/rirekisyo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B79CEFF6-220E-4713-A960-767E0352042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{B79CEFF6-220E-4713-A960-767E0352042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53468F09-E100-41CD-A2AB-71BF1D256CC2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>履　歴　書</t>
     <rPh sb="0" eb="1">
@@ -279,6 +279,10 @@
   <si>
     <t xml:space="preserve">E-mail
 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1666,7 +1670,9 @@
       <c r="P6" s="36"/>
     </row>
     <row r="7" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="29"/>
+      <c r="B7" s="29" t="s">
+        <v>22</v>
+      </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>

--- a/rirekisyo.xlsx
+++ b/rirekisyo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{B79CEFF6-220E-4713-A960-767E0352042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53468F09-E100-41CD-A2AB-71BF1D256CC2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4150" yWindow="630" windowWidth="14550" windowHeight="8980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A4サイズ" sheetId="5" r:id="rId1"/>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="5" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="70" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5" s="71"/>
       <c r="D5" s="72"/>
